--- a/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
+++ b/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T15:15:09+00:00</t>
+    <t>2026-07-01T08:10:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
+++ b/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:10:30+00:00</t>
+    <t>2026-07-16T07:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
+++ b/mapping/ig/CdaCECSCDToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T07:55:09+00:00</t>
+    <t>2026-07-16T08:29:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
